--- a/docs/acc/fuel calc.xlsx
+++ b/docs/acc/fuel calc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2a1bbde8808ab92/Setup Forge/ACC Setup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piero\Documents\GitHub\sim-racing-setups\docs\acc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="590" documentId="8_{B12D287D-8713-457F-B976-642F3227D37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2358EE28-B0B5-43EB-A123-289BEAD6D4A2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984BF138-FA69-40F9-899C-19739A94AB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A39CC2B-4FC0-4D5D-A9F2-57B9377746D6}"/>
   </bookViews>
@@ -314,9 +314,6 @@
     <t>3.66</t>
   </si>
   <si>
-    <t>FORD MUSTANG</t>
-  </si>
-  <si>
     <t>3.24</t>
   </si>
   <si>
@@ -507,6 +504,9 @@
   </si>
   <si>
     <t>PORSCHE 991 II GT3 R</t>
+  </si>
+  <si>
+    <t>FORD MUSTANG GT3</t>
   </si>
 </sst>
 </file>
@@ -946,7 +946,7 @@
     <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="29" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="25.77734375" bestFit="1" customWidth="1"/>
@@ -985,79 +985,79 @@
         <v>72</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>77</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>85</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="P1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="AC1" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
@@ -1086,7 +1086,7 @@
         <v>57</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>78</v>
@@ -1095,10 +1095,10 @@
         <v>78</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>10</v>
@@ -1113,10 +1113,10 @@
         <v>48</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>78</v>
@@ -1125,7 +1125,7 @@
         <v>78</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>78</v>
@@ -1149,10 +1149,10 @@
         <v>81</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AF3" s="1" t="s">
         <v>54</v>
@@ -1184,7 +1184,7 @@
         <v>57</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>43</v>
@@ -1193,10 +1193,10 @@
         <v>43</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>10</v>
@@ -1223,7 +1223,7 @@
         <v>16</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>78</v>
@@ -1247,10 +1247,10 @@
         <v>81</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AF4" s="1" t="s">
         <v>3</v>
@@ -1315,10 +1315,10 @@
         <v>87</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>87</v>
@@ -1339,7 +1339,7 @@
         <v>6</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>28</v>
@@ -1351,7 +1351,7 @@
         <v>87</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
@@ -1401,10 +1401,10 @@
         <v>50</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>48</v>
@@ -1526,25 +1526,25 @@
         <v>48</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AB7" s="3" t="s">
         <v>62</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AF7" s="1" t="s">
         <v>3</v>
@@ -1603,10 +1603,10 @@
         <v>81</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>49</v>
@@ -1618,19 +1618,19 @@
         <v>37</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>10</v>
@@ -1713,7 +1713,7 @@
         <v>42</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>55</v>
@@ -1772,10 +1772,10 @@
         <v>57</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>78</v>
@@ -1811,7 +1811,7 @@
         <v>78</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>86</v>
@@ -1835,10 +1835,10 @@
         <v>81</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>54</v>
@@ -1927,7 +1927,7 @@
         <v>62</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AC11" s="1" t="s">
         <v>48</v>
@@ -1977,10 +1977,10 @@
         <v>69</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>40</v>
@@ -2075,10 +2075,10 @@
         <v>79</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>47</v>
@@ -2129,10 +2129,10 @@
         <v>79</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF13" s="1" t="s">
         <v>79</v>
@@ -2206,13 +2206,13 @@
         <v>87</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Z14" s="1" t="s">
         <v>28</v>
@@ -2301,22 +2301,22 @@
         <v>81</v>
       </c>
       <c r="V15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="W15" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="W15" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="X15" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Z15" s="1" t="s">
         <v>49</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>55</v>
@@ -2325,111 +2325,111 @@
         <v>87</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="V16" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="W16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z16" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="AA16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC16" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="N16" s="4" t="s">
+      <c r="AD16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AE16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF16" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="R16" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="S16" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="T16" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="U16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="V16" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="W16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="X16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z16" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="AB16" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AC16" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE16" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="AF16" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.3">
@@ -2458,7 +2458,7 @@
         <v>76</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>62</v>
@@ -2518,7 +2518,7 @@
         <v>73</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AD17" s="1" t="s">
         <v>55</v>
@@ -2527,7 +2527,7 @@
         <v>55</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.3">
@@ -2556,7 +2556,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>6</v>
@@ -2565,10 +2565,10 @@
         <v>6</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>90</v>
@@ -2595,7 +2595,7 @@
         <v>6</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>81</v>
@@ -2616,13 +2616,13 @@
         <v>10</v>
       </c>
       <c r="AC18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD18" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="AD18" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="AE18" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF18" s="1" t="s">
         <v>28</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>40</v>
@@ -2666,7 +2666,7 @@
         <v>42</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N19" s="4" t="s">
         <v>48</v>
@@ -2678,7 +2678,7 @@
         <v>84</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R19" s="4" t="s">
         <v>40</v>
@@ -2708,7 +2708,7 @@
         <v>48</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AB19" s="5" t="s">
         <v>26</v>
@@ -2752,7 +2752,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>59</v>
@@ -2791,7 +2791,7 @@
         <v>59</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>58</v>
@@ -2812,7 +2812,7 @@
         <v>10</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD20" s="1" t="s">
         <v>6</v>
@@ -2904,7 +2904,7 @@
         <v>48</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>62</v>
@@ -2948,7 +2948,7 @@
         <v>20</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>82</v>
@@ -2975,10 +2975,10 @@
         <v>79</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>82</v>
@@ -2987,28 +2987,28 @@
         <v>82</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z22" s="1" t="s">
         <v>82</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AD22" s="1" t="s">
         <v>61</v>
@@ -3017,7 +3017,7 @@
         <v>61</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.3">
@@ -3201,16 +3201,16 @@
         <v>59</v>
       </c>
       <c r="AB24" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>83</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>83</v>
@@ -3245,7 +3245,7 @@
         <v>37</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>37</v>
@@ -3305,10 +3305,10 @@
         <v>37</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF25" s="1" t="s">
         <v>83</v>
@@ -3382,10 +3382,10 @@
         <v>86</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y26" s="1" t="s">
         <v>78</v>
@@ -3394,19 +3394,19 @@
         <v>78</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>62</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AF26" s="1" t="s">
         <v>3</v>
@@ -3447,10 +3447,10 @@
         <v>55</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>48</v>
@@ -3459,10 +3459,10 @@
         <v>48</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>48</v>
@@ -3492,7 +3492,7 @@
         <v>48</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>26</v>
